--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:03+00:00</t>
+    <t>2023-03-24T14:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:14+00:00</t>
+    <t>2023-03-24T14:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:11+00:00</t>
+    <t>2023-03-24T14:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:59+00:00</t>
+    <t>2023-03-24T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:20+00:00</t>
+    <t>2023-03-24T15:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:53+00:00</t>
+    <t>2023-03-26T08:42:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="578">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:42:47+00:00</t>
+    <t>2023-03-26T09:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -978,6 +978,9 @@
   </si>
   <si>
     <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>Patient folder number</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -6415,7 +6418,7 @@
         <v>80</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>80</v>
+        <v>313</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>80</v>
@@ -6454,7 +6457,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6469,7 +6472,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>80</v>
@@ -6478,7 +6481,7 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6486,7 +6489,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>202</v>
@@ -6531,7 +6534,7 @@
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>80</v>
@@ -6605,7 +6608,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>213</v>
@@ -6722,7 +6725,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>222</v>
@@ -6837,7 +6840,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>230</v>
@@ -6954,10 +6957,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6983,67 +6986,67 @@
         <v>299</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="R42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="P42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q42" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="R42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7058,13 +7061,13 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>171</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
@@ -7075,10 +7078,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7101,19 +7104,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7162,7 +7165,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7177,16 +7180,16 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7194,10 +7197,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7309,10 +7312,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7426,10 +7429,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7455,16 +7458,16 @@
         <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7492,10 +7495,10 @@
         <v>184</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7513,7 +7516,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7528,7 +7531,7 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>80</v>
@@ -7537,7 +7540,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7545,10 +7548,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7574,16 +7577,16 @@
         <v>167</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7632,7 +7635,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7647,7 +7650,7 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>80</v>
@@ -7656,7 +7659,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7664,14 +7667,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7693,13 +7696,13 @@
         <v>167</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7749,7 +7752,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7764,7 +7767,7 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>80</v>
@@ -7773,7 +7776,7 @@
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7781,14 +7784,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7810,13 +7813,13 @@
         <v>167</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7866,7 +7869,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7881,7 +7884,7 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>80</v>
@@ -7890,7 +7893,7 @@
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -7898,10 +7901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7927,10 +7930,10 @@
         <v>167</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7981,7 +7984,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7996,7 +7999,7 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>80</v>
@@ -8005,7 +8008,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8013,10 +8016,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8042,10 +8045,10 @@
         <v>167</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8096,7 +8099,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8111,7 +8114,7 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>80</v>
@@ -8120,7 +8123,7 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8128,10 +8131,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8157,14 +8160,14 @@
         <v>223</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8213,7 +8216,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8228,7 +8231,7 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>80</v>
@@ -8237,7 +8240,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8245,10 +8248,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8271,19 +8274,19 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8332,7 +8335,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8347,16 +8350,16 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8364,10 +8367,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8393,16 +8396,16 @@
         <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8430,10 +8433,10 @@
         <v>184</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -8451,7 +8454,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8466,16 +8469,16 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8483,10 +8486,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8509,19 +8512,19 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8570,7 +8573,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8585,27 +8588,27 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8628,19 +8631,19 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8689,7 +8692,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8704,7 +8707,7 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>171</v>
@@ -8713,7 +8716,7 @@
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -8721,10 +8724,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8747,19 +8750,19 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8808,7 +8811,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8823,16 +8826,16 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -8840,10 +8843,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8869,14 +8872,14 @@
         <v>191</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8904,10 +8907,10 @@
         <v>196</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8925,7 +8928,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8940,16 +8943,16 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8957,10 +8960,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8983,19 +8986,19 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9044,7 +9047,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9059,7 +9062,7 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>171</v>
@@ -9068,7 +9071,7 @@
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
@@ -9076,10 +9079,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9102,19 +9105,19 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9163,7 +9166,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9178,7 +9181,7 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>171</v>
@@ -9187,7 +9190,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9195,10 +9198,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9221,19 +9224,19 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9282,7 +9285,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9294,10 +9297,10 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>171</v>
@@ -9314,10 +9317,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9429,10 +9432,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9546,14 +9549,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9575,10 +9578,10 @@
         <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>149</v>
@@ -9633,7 +9636,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9665,10 +9668,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9694,14 +9697,14 @@
         <v>191</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9729,10 +9732,10 @@
         <v>196</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -9750,7 +9753,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9765,7 +9768,7 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>171</v>
@@ -9774,7 +9777,7 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -9782,10 +9785,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9808,17 +9811,17 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9867,7 +9870,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9882,7 +9885,7 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>171</v>
@@ -9891,7 +9894,7 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -9899,10 +9902,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9925,19 +9928,19 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -9986,7 +9989,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10001,7 +10004,7 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>171</v>
@@ -10010,7 +10013,7 @@
         <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
@@ -10018,10 +10021,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10044,17 +10047,17 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10103,7 +10106,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10118,7 +10121,7 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>171</v>
@@ -10127,7 +10130,7 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -10135,10 +10138,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10164,14 +10167,14 @@
         <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10199,10 +10202,10 @@
         <v>184</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
@@ -10220,7 +10223,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10235,7 +10238,7 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>171</v>
@@ -10244,7 +10247,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -10252,10 +10255,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10281,14 +10284,14 @@
         <v>231</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10337,7 +10340,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10346,13 +10349,13 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>171</v>
@@ -10361,7 +10364,7 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10369,10 +10372,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10398,10 +10401,10 @@
         <v>223</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10452,7 +10455,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10467,7 +10470,7 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>171</v>
@@ -10484,10 +10487,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10510,19 +10513,19 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -10571,7 +10574,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10586,10 +10589,10 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>80</v>
@@ -10603,10 +10606,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10718,10 +10721,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10835,14 +10838,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10864,10 +10867,10 @@
         <v>132</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>149</v>
@@ -10922,7 +10925,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10954,10 +10957,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10983,16 +10986,16 @@
         <v>191</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11041,7 +11044,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -11056,16 +11059,16 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11073,10 +11076,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11102,16 +11105,16 @@
         <v>299</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11160,7 +11163,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11175,16 +11178,16 @@
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -11192,14 +11195,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11218,16 +11221,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11277,7 +11280,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11292,7 +11295,7 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>171</v>
@@ -11301,7 +11304,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11309,10 +11312,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11338,16 +11341,16 @@
         <v>231</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11396,7 +11399,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11411,10 +11414,10 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>80</v>
@@ -11428,10 +11431,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11454,19 +11457,19 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11515,7 +11518,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11530,7 +11533,7 @@
         <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>171</v>
@@ -11547,10 +11550,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11662,10 +11665,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11779,14 +11782,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11808,10 +11811,10 @@
         <v>132</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>149</v>
@@ -11866,7 +11869,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11898,10 +11901,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11924,16 +11927,16 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11983,7 +11986,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>87</v>
@@ -12007,7 +12010,7 @@
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12015,10 +12018,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12044,10 +12047,10 @@
         <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12077,10 +12080,10 @@
         <v>184</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
@@ -12098,7 +12101,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>87</v>
@@ -12113,7 +12116,7 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>171</v>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:01:05+00:00</t>
+    <t>2023-03-26T09:02:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:02:01+00:00</t>
+    <t>2023-03-26T10:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:39+00:00</t>
+    <t>2023-03-26T10:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:51+00:00</t>
+    <t>2023-03-26T11:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:08:41+00:00</t>
+    <t>2023-03-26T11:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:16:53+00:00</t>
+    <t>2023-03-26T11:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3975" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:17:47+00:00</t>
+    <t>2023-03-27T11:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1371,6 +1371,256 @@
     <t>PID-11</t>
   </si>
   <si>
+    <t>Patient.address.id</t>
+  </si>
+  <si>
+    <t>Patient.address.extension</t>
+  </si>
+  <si>
+    <t>Patient.address.use</t>
+  </si>
+  <si>
+    <t>home | work | temp | old | billing - purpose of this address</t>
+  </si>
+  <si>
+    <t>The purpose of this address.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an address is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows an appropriate address to be chosen from a list of many.</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>The use of an address.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Address.use</t>
+  </si>
+  <si>
+    <t>XAD.7</t>
+  </si>
+  <si>
+    <t>Patient.address.type</t>
+  </si>
+  <si>
+    <t>postal | physical | both</t>
+  </si>
+  <si>
+    <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
+  </si>
+  <si>
+    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>The type of an address (physical / postal).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Address.type</t>
+  </si>
+  <si>
+    <t>XAD.18</t>
+  </si>
+  <si>
+    <t>Patient.address.text</t>
+  </si>
+  <si>
+    <t>Text representation of the address</t>
+  </si>
+  <si>
+    <t>Specifies the entire address as it should be displayed e.g. on a postal label. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating an address SHALL ensure that  when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>137 Nowhere Street, Erewhon 9132</t>
+  </si>
+  <si>
+    <t>Address.text</t>
+  </si>
+  <si>
+    <t>XAD.1 + XAD.2 + XAD.3 + XAD.4 + XAD.5 + XAD.6</t>
+  </si>
+  <si>
+    <t>Patient.address.line</t>
+  </si>
+  <si>
+    <t>Street name, number, direction &amp; P.O. Box etc.</t>
+  </si>
+  <si>
+    <t>This component contains the house number, apartment number, street name, street direction,  P.O. Box number, delivery hints, and similar address information.</t>
+  </si>
+  <si>
+    <t>137 Nowhere Street</t>
+  </si>
+  <si>
+    <t>Address.line</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = AL]</t>
+  </si>
+  <si>
+    <t>XAD.1 + XAD.2 (note: XAD.1 and XAD.2 have different meanings for a company address than for a person address)</t>
+  </si>
+  <si>
+    <t>Patient.address.city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municpality
+</t>
+  </si>
+  <si>
+    <t>Name of city, town etc.</t>
+  </si>
+  <si>
+    <t>The name of the city, town, suburb, village or other community or delivery center.</t>
+  </si>
+  <si>
+    <t>Erewhon</t>
+  </si>
+  <si>
+    <t>Address.city</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CTY]</t>
+  </si>
+  <si>
+    <t>XAD.3</t>
+  </si>
+  <si>
+    <t>Patient.address.district</t>
+  </si>
+  <si>
+    <t xml:space="preserve">County
+</t>
+  </si>
+  <si>
+    <t>District name (aka county)</t>
+  </si>
+  <si>
+    <t>The name of the administrative area (county).</t>
+  </si>
+  <si>
+    <t>District is sometimes known as county, but in some regions 'county' is used in place of city (municipality), so county name should be conveyed in city instead.</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>Address.district</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CNT | CPA]</t>
+  </si>
+  <si>
+    <t>XAD.9</t>
+  </si>
+  <si>
+    <t>Patient.address.state</t>
+  </si>
+  <si>
+    <t>Province
+Territory</t>
+  </si>
+  <si>
+    <t>Sub-unit of country (abbreviations ok)</t>
+  </si>
+  <si>
+    <t>Sub-unit of a country with limited sovereignty in a federally organized country. A code may be used if codes are in common use (e.g. US 2 letter state codes).</t>
+  </si>
+  <si>
+    <t>Address.state</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = STA]</t>
+  </si>
+  <si>
+    <t>XAD.4</t>
+  </si>
+  <si>
+    <t>Patient.address.postalCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zip
+</t>
+  </si>
+  <si>
+    <t>Postal code for area</t>
+  </si>
+  <si>
+    <t>A postal code designating a region defined by the postal service.</t>
+  </si>
+  <si>
+    <t>9132</t>
+  </si>
+  <si>
+    <t>Address.postalCode</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = ZIP]</t>
+  </si>
+  <si>
+    <t>XAD.5</t>
+  </si>
+  <si>
+    <t>Patient.address.country</t>
+  </si>
+  <si>
+    <t>Country (e.g. can be ISO 3166 2 or 3 letter code)</t>
+  </si>
+  <si>
+    <t>Country - a nation as commonly understood or generally accepted.</t>
+  </si>
+  <si>
+    <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
+  </si>
+  <si>
+    <t>Address.country</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CNT]</t>
+  </si>
+  <si>
+    <t>XAD.6</t>
+  </si>
+  <si>
+    <t>Patient.address.period</t>
+  </si>
+  <si>
+    <t>Time period when address was/is in use</t>
+  </si>
+  <si>
+    <t>Time period when address was/is in use.</t>
+  </si>
+  <si>
+    <t>Allows addresses to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>&lt;valuePeriod xmlns="http://hl7.org/fhir"&gt;
+  &lt;start value="2010-03-23"/&gt;
+  &lt;end value="2010-07-01"/&gt;
+&lt;/valuePeriod&gt;</t>
+  </si>
+  <si>
+    <t>Address.period</t>
+  </si>
+  <si>
+    <t>XAD.12 / XAD.13 + XAD.14</t>
+  </si>
+  <si>
     <t>Patient.maritalStatus</t>
   </si>
   <si>
@@ -1537,6 +1787,33 @@
   </si>
   <si>
     <t>NK1-2</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.use</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.text</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.family</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.given</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.prefix</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.suffix</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.period</t>
   </si>
   <si>
     <t>Patient.contact.telecom</t>
@@ -2101,7 +2378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO85"/>
+  <dimension ref="A1:AO106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.7109375" customWidth="true" bestFit="true"/>
@@ -2123,7 +2400,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="39.97265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -2142,7 +2419,7 @@
     <col min="37" max="37" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="40.8125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="56.17578125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="40.0703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -8854,7 +9131,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>87</v>
@@ -8869,18 +9146,16 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>441</v>
+        <v>168</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>442</v>
+        <v>169</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>443</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8904,13 +9179,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>444</v>
+        <v>80</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>445</v>
+        <v>80</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8928,7 +9203,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>440</v>
+        <v>170</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8940,19 +9215,19 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>446</v>
+        <v>171</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>447</v>
+        <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>448</v>
+        <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8960,21 +9235,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -8986,20 +9261,18 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>450</v>
+        <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>174</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
+        <v>175</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -9035,43 +9308,43 @@
         <v>80</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>177</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>455</v>
+        <v>171</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>456</v>
+        <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
@@ -9079,10 +9352,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9093,31 +9366,31 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9130,7 +9403,7 @@
         <v>80</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>80</v>
@@ -9142,13 +9415,13 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>80</v>
+        <v>448</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -9166,13 +9439,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -9181,16 +9454,16 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>463</v>
+        <v>349</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9198,10 +9471,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9212,7 +9485,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
@@ -9221,23 +9494,21 @@
         <v>80</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>466</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9249,7 +9520,7 @@
         <v>80</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>80</v>
+        <v>456</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>80</v>
@@ -9261,13 +9532,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>80</v>
+        <v>457</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9285,31 +9556,31 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>471</v>
+        <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>472</v>
+        <v>349</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9317,10 +9588,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9340,19 +9611,23 @@
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>167</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>168</v>
+        <v>462</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9364,7 +9639,7 @@
         <v>80</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>80</v>
+        <v>465</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>80</v>
@@ -9400,7 +9675,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>170</v>
+        <v>466</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9412,10 +9687,10 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>171</v>
+        <v>357</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>80</v>
@@ -9424,7 +9699,7 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>80</v>
+        <v>467</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9432,18 +9707,18 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>79</v>
@@ -9455,20 +9730,18 @@
         <v>80</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>174</v>
+        <v>469</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9481,7 +9754,7 @@
         <v>80</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>80</v>
+        <v>471</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>80</v>
@@ -9517,7 +9790,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>177</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9529,10 +9802,10 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>171</v>
+        <v>473</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>80</v>
@@ -9541,7 +9814,7 @@
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>80</v>
+        <v>474</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9560,22 +9833,22 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>477</v>
@@ -9583,12 +9856,8 @@
       <c r="M64" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9600,7 +9869,7 @@
         <v>80</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>80</v>
+        <v>479</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>80</v>
@@ -9636,22 +9905,22 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>130</v>
+        <v>481</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>80</v>
@@ -9660,7 +9929,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>80</v>
+        <v>482</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9668,21 +9937,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>80</v>
+        <v>484</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
@@ -9691,21 +9960,21 @@
         <v>80</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
@@ -9717,7 +9986,7 @@
         <v>80</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>80</v>
+        <v>488</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>80</v>
@@ -9729,13 +9998,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>484</v>
+        <v>80</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>485</v>
+        <v>80</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -9753,13 +10022,13 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
@@ -9768,16 +10037,16 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -9785,18 +10054,18 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>80</v>
+        <v>493</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>87</v>
@@ -9808,21 +10077,19 @@
         <v>80</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>331</v>
+        <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>491</v>
-      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>80</v>
       </c>
@@ -9870,7 +10137,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9885,16 +10152,16 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>336</v>
+        <v>497</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -9902,21 +10169,21 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>80</v>
@@ -9925,23 +10192,19 @@
         <v>80</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>395</v>
+        <v>167</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>80</v>
       </c>
@@ -9953,7 +10216,7 @@
         <v>80</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>80</v>
+        <v>503</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>80</v>
@@ -9989,13 +10252,13 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>80</v>
@@ -10004,16 +10267,16 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>400</v>
+        <v>505</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
@@ -10021,10 +10284,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10032,7 +10295,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>87</v>
@@ -10044,21 +10307,21 @@
         <v>80</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>432</v>
+        <v>167</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
@@ -10106,7 +10369,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10121,16 +10384,16 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>437</v>
+        <v>512</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -10138,10 +10401,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10161,20 +10424,20 @@
         <v>80</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>404</v>
+        <v>515</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10187,7 +10450,7 @@
         <v>80</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>80</v>
+        <v>518</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>80</v>
@@ -10199,13 +10462,13 @@
         <v>80</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
@@ -10223,7 +10486,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10238,16 +10501,16 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -10255,10 +10518,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10266,7 +10529,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>87</v>
@@ -10281,17 +10544,17 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10316,13 +10579,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>80</v>
+        <v>525</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>80</v>
+        <v>526</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10340,7 +10603,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10349,22 +10612,22 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>511</v>
+        <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>171</v>
+        <v>528</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10372,10 +10635,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10398,16 +10661,20 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>223</v>
+        <v>531</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
       </c>
@@ -10455,7 +10722,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10470,7 +10737,7 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>171</v>
@@ -10479,7 +10746,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>80</v>
+        <v>537</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10487,10 +10754,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10513,19 +10780,19 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>466</v>
+        <v>539</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -10574,7 +10841,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10589,16 +10856,16 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>524</v>
+        <v>171</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>80</v>
+        <v>545</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
@@ -10606,10 +10873,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10620,7 +10887,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>80</v>
@@ -10632,16 +10899,20 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>167</v>
+        <v>547</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>168</v>
+        <v>548</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
       </c>
@@ -10689,25 +10960,25 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>170</v>
+        <v>546</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>80</v>
+        <v>552</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>80</v>
@@ -10721,21 +10992,21 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
@@ -10747,17 +11018,15 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -10806,19 +11075,19 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>171</v>
@@ -10838,14 +11107,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>476</v>
+        <v>146</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10858,26 +11127,24 @@
         <v>80</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>477</v>
+        <v>174</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>478</v>
+        <v>175</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O75" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>80</v>
       </c>
@@ -10925,7 +11192,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>479</v>
+        <v>177</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10940,7 +11207,7 @@
         <v>138</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>80</v>
@@ -10957,45 +11224,45 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>80</v>
+        <v>557</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>529</v>
+        <v>558</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>530</v>
+        <v>559</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>531</v>
+        <v>149</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>532</v>
+        <v>150</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11020,13 +11287,13 @@
         <v>80</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>80</v>
@@ -11044,31 +11311,31 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>528</v>
+        <v>560</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>533</v>
+        <v>130</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>534</v>
+        <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>535</v>
+        <v>80</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11076,10 +11343,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11087,7 +11354,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>87</v>
@@ -11102,19 +11369,17 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>299</v>
+        <v>191</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>540</v>
+        <v>564</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11139,13 +11404,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>80</v>
+        <v>565</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>80</v>
+        <v>566</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11163,13 +11428,13 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>80</v>
@@ -11178,16 +11443,16 @@
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>542</v>
+        <v>171</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -11195,21 +11460,21 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>545</v>
+        <v>80</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
@@ -11221,18 +11486,18 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>546</v>
+        <v>331</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>547</v>
+        <v>570</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11280,13 +11545,13 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>80</v>
@@ -11295,7 +11560,7 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>550</v>
+        <v>336</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>171</v>
@@ -11304,7 +11569,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11312,10 +11577,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>552</v>
+        <v>574</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>552</v>
+        <v>574</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11323,7 +11588,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>87</v>
@@ -11335,23 +11600,19 @@
         <v>80</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>553</v>
+        <v>168</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>80</v>
       </c>
@@ -11399,7 +11660,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>552</v>
+        <v>170</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11411,13 +11672,13 @@
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>512</v>
+        <v>171</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>557</v>
+        <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>80</v>
@@ -11431,14 +11692,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11451,26 +11712,24 @@
         <v>80</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>466</v>
+        <v>132</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>559</v>
+        <v>174</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>560</v>
+        <v>175</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
       </c>
@@ -11506,19 +11765,19 @@
         <v>80</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>558</v>
+        <v>177</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11530,13 +11789,13 @@
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>563</v>
+        <v>171</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>80</v>
@@ -11550,10 +11809,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11570,22 +11829,26 @@
         <v>80</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>168</v>
+        <v>342</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
       </c>
@@ -11609,13 +11872,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -11633,7 +11896,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>170</v>
+        <v>348</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11645,10 +11908,10 @@
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>171</v>
+        <v>349</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>80</v>
@@ -11657,7 +11920,7 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -11665,21 +11928,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -11688,21 +11951,23 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>174</v>
+        <v>352</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>175</v>
+        <v>353</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
       </c>
@@ -11750,22 +12015,22 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>177</v>
+        <v>356</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>171</v>
+        <v>357</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>80</v>
@@ -11774,7 +12039,7 @@
         <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -11782,46 +12047,44 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>476</v>
+        <v>360</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>477</v>
+        <v>361</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>478</v>
+        <v>362</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>80</v>
       </c>
@@ -11869,22 +12132,22 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>479</v>
+        <v>364</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>130</v>
+        <v>365</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>80</v>
@@ -11893,7 +12156,7 @@
         <v>80</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>80</v>
+        <v>366</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -11901,21 +12164,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>87</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -11927,16 +12190,16 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>568</v>
+        <v>167</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>569</v>
+        <v>369</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>570</v>
+        <v>370</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>571</v>
+        <v>371</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11986,13 +12249,13 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>567</v>
+        <v>372</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
@@ -12001,16 +12264,16 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>159</v>
+        <v>373</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>572</v>
+        <v>374</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12018,10 +12281,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12029,10 +12292,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12044,13 +12307,13 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>574</v>
+        <v>376</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>575</v>
+        <v>377</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12077,13 +12340,13 @@
         <v>80</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>575</v>
+        <v>80</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>576</v>
+        <v>80</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
@@ -12101,13 +12364,13 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>573</v>
+        <v>378</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
@@ -12116,18 +12379,2481 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>577</v>
+        <v>379</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL88" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AM85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO85" t="s" s="2">
+      <c r="AM88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO106" t="s" s="2">
         <v>80</v>
       </c>
     </row>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:35:12+00:00</t>
+    <t>2023-03-27T12:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:01:10+00:00</t>
+    <t>2023-03-27T12:02:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:02:15+00:00</t>
+    <t>2023-03-28T07:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:37:59+00:00</t>
+    <t>2023-03-28T07:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:45:58+00:00</t>
+    <t>2023-03-29T10:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:46:03+00:00</t>
+    <t>2023-03-29T10:52:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3975" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3975" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:52:43+00:00</t>
+    <t>2023-03-31T13:54:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1760,6 +1760,13 @@
   </si>
   <si>
     <t>Used to determine which contact person is the most relevant to approach, depending on circumstances.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="N"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
@@ -11354,10 +11361,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>80</v>
@@ -11389,7 +11396,7 @@
         <v>80</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>80</v>
+        <v>565</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>80</v>
@@ -11407,10 +11414,10 @@
         <v>196</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11443,7 +11450,7 @@
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>171</v>
@@ -11452,7 +11459,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -11460,10 +11467,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11489,14 +11496,14 @@
         <v>331</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11545,7 +11552,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11569,7 +11576,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11577,10 +11584,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11692,10 +11699,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11809,10 +11816,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11928,10 +11935,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12047,10 +12054,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12164,10 +12171,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12281,10 +12288,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12396,10 +12403,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12511,10 +12518,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12628,10 +12635,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12657,13 +12664,13 @@
         <v>395</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>399</v>
@@ -12715,7 +12722,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12739,7 +12746,7 @@
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -12747,10 +12754,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12776,14 +12783,14 @@
         <v>432</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -12832,7 +12839,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12856,7 +12863,7 @@
         <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -12864,10 +12871,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12896,11 +12903,11 @@
         <v>404</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -12949,7 +12956,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12973,7 +12980,7 @@
         <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -12981,10 +12988,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13010,14 +13017,14 @@
         <v>231</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13066,7 +13073,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13075,13 +13082,13 @@
         <v>87</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>171</v>
@@ -13090,7 +13097,7 @@
         <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13098,10 +13105,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13127,10 +13134,10 @@
         <v>223</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13181,7 +13188,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13196,7 +13203,7 @@
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>171</v>
@@ -13213,10 +13220,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13242,16 +13249,16 @@
         <v>547</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13300,7 +13307,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13315,10 +13322,10 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>80</v>
@@ -13332,10 +13339,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13447,10 +13454,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13564,10 +13571,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13683,10 +13690,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13712,16 +13719,16 @@
         <v>191</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>80</v>
@@ -13770,7 +13777,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>87</v>
@@ -13785,16 +13792,16 @@
         <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>80</v>
@@ -13802,10 +13809,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13831,16 +13838,16 @@
         <v>299</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -13889,7 +13896,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13904,16 +13911,16 @@
         <v>99</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -13921,14 +13928,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13947,16 +13954,16 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14006,7 +14013,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14021,7 +14028,7 @@
         <v>99</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>171</v>
@@ -14030,7 +14037,7 @@
         <v>80</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14038,10 +14045,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14067,16 +14074,16 @@
         <v>231</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14125,7 +14132,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14140,10 +14147,10 @@
         <v>99</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>80</v>
@@ -14157,10 +14164,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14186,16 +14193,16 @@
         <v>547</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14244,7 +14251,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14259,7 +14266,7 @@
         <v>99</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>171</v>
@@ -14276,10 +14283,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14391,10 +14398,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14508,10 +14515,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14627,10 +14634,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14653,16 +14660,16 @@
         <v>88</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14712,7 +14719,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>87</v>
@@ -14736,7 +14743,7 @@
         <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -14744,10 +14751,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14773,10 +14780,10 @@
         <v>107</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14806,10 +14813,10 @@
         <v>184</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>80</v>
@@ -14827,7 +14834,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>87</v>
@@ -14842,7 +14849,7 @@
         <v>99</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>171</v>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:54:07+00:00</t>
+    <t>2023-03-31T13:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3975" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4384" uniqueCount="681">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:55:03+00:00</t>
+    <t>2023-04-01T08:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1779,6 +1779,42 @@
   </si>
   <si>
     <t>NK1-7, NK1-3</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.system</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0131</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.version</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.code</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.display</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.text</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -2385,11 +2421,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO106"/>
+  <dimension ref="A1:AO117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.23828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.59375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.59375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -11493,18 +11529,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>331</v>
+        <v>167</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>571</v>
+        <v>168</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>572</v>
+        <v>169</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>573</v>
-      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11552,7 +11586,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>570</v>
+        <v>170</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11564,19 +11598,19 @@
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>336</v>
+        <v>171</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>574</v>
+        <v>80</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11584,21 +11618,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>80</v>
@@ -11610,15 +11644,17 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11655,31 +11691,31 @@
         <v>80</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>171</v>
@@ -11699,14 +11735,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11722,21 +11758,23 @@
         <v>80</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>132</v>
+        <v>250</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>174</v>
+        <v>251</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>175</v>
+        <v>252</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
       </c>
@@ -11772,19 +11810,19 @@
         <v>80</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>177</v>
+        <v>255</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11796,10 +11834,10 @@
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>80</v>
@@ -11808,7 +11846,7 @@
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -11816,10 +11854,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11836,26 +11874,22 @@
         <v>80</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>342</v>
+        <v>168</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>80</v>
       </c>
@@ -11879,13 +11913,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -11903,7 +11937,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>348</v>
+        <v>170</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11915,10 +11949,10 @@
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>349</v>
+        <v>171</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>80</v>
@@ -11927,7 +11961,7 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -11935,21 +11969,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -11958,23 +11992,21 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>352</v>
+        <v>174</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>353</v>
+        <v>175</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>80</v>
       </c>
@@ -12010,34 +12042,34 @@
         <v>80</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>356</v>
+        <v>177</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>357</v>
+        <v>171</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>80</v>
@@ -12046,7 +12078,7 @@
         <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>358</v>
+        <v>80</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12054,18 +12086,18 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>360</v>
+        <v>80</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>87</v>
@@ -12080,18 +12112,20 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>361</v>
+        <v>264</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>362</v>
+        <v>265</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
       </c>
@@ -12100,7 +12134,7 @@
         <v>80</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>80</v>
+        <v>576</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>80</v>
@@ -12139,7 +12173,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>364</v>
+        <v>269</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12154,7 +12188,7 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>365</v>
+        <v>270</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>80</v>
@@ -12163,7 +12197,7 @@
         <v>80</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>366</v>
+        <v>271</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12171,21 +12205,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>368</v>
+        <v>80</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -12200,13 +12234,13 @@
         <v>167</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>369</v>
+        <v>274</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>370</v>
+        <v>275</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>371</v>
+        <v>276</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12256,13 +12290,13 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>372</v>
+        <v>277</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
@@ -12271,7 +12305,7 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>373</v>
+        <v>278</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>80</v>
@@ -12280,7 +12314,7 @@
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>374</v>
+        <v>279</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12288,10 +12322,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12302,7 +12336,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12314,16 +12348,18 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>376</v>
+        <v>282</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>377</v>
+        <v>283</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
       </c>
@@ -12371,13 +12407,13 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>378</v>
+        <v>285</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
@@ -12386,7 +12422,7 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>379</v>
+        <v>286</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>80</v>
@@ -12395,7 +12431,7 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
@@ -12403,10 +12439,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12417,7 +12453,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>80</v>
@@ -12432,13 +12468,15 @@
         <v>167</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>382</v>
+        <v>290</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>383</v>
+        <v>291</v>
       </c>
       <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
       </c>
@@ -12486,13 +12524,13 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>384</v>
+        <v>294</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>80</v>
@@ -12501,7 +12539,7 @@
         <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>385</v>
+        <v>295</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
@@ -12510,7 +12548,7 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>386</v>
+        <v>296</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -12518,10 +12556,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12544,17 +12582,19 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>388</v>
+        <v>300</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O87" t="s" s="2">
-        <v>390</v>
+        <v>303</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12603,7 +12643,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>391</v>
+        <v>304</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12618,7 +12658,7 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>392</v>
+        <v>305</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>80</v>
@@ -12627,7 +12667,7 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>393</v>
+        <v>306</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -12635,10 +12675,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12649,7 +12689,7 @@
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>80</v>
@@ -12658,22 +12698,22 @@
         <v>80</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>395</v>
+        <v>167</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>585</v>
+        <v>309</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>586</v>
+        <v>310</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>587</v>
+        <v>311</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>399</v>
+        <v>312</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -12722,13 +12762,13 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>584</v>
+        <v>314</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
@@ -12737,16 +12777,16 @@
         <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>400</v>
+        <v>315</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>588</v>
+        <v>316</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -12754,10 +12794,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12780,17 +12820,17 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>432</v>
+        <v>331</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -12839,7 +12879,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12854,7 +12894,7 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>437</v>
+        <v>336</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>171</v>
@@ -12863,7 +12903,7 @@
         <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -12871,10 +12911,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12897,18 +12937,16 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>404</v>
+        <v>168</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>595</v>
+        <v>169</v>
       </c>
       <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>596</v>
-      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>80</v>
       </c>
@@ -12932,13 +12970,13 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -12956,7 +12994,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>594</v>
+        <v>170</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12968,19 +13006,19 @@
         <v>80</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>410</v>
+        <v>171</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>597</v>
+        <v>80</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -12988,21 +13026,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>80</v>
@@ -13014,18 +13052,18 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>231</v>
+        <v>132</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>599</v>
+        <v>174</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13061,43 +13099,43 @@
         <v>80</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>598</v>
+        <v>177</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>602</v>
+        <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>603</v>
+        <v>171</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>604</v>
+        <v>80</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13105,10 +13143,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13125,22 +13163,26 @@
         <v>80</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>223</v>
+        <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>606</v>
+        <v>342</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
       </c>
@@ -13164,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -13188,7 +13230,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>605</v>
+        <v>348</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13203,16 +13245,16 @@
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>608</v>
+        <v>349</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13220,10 +13262,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>609</v>
+        <v>590</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>609</v>
+        <v>590</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13234,7 +13276,7 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>80</v>
@@ -13243,22 +13285,22 @@
         <v>80</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>547</v>
+        <v>167</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>610</v>
+        <v>352</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>611</v>
+        <v>353</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>612</v>
+        <v>354</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>613</v>
+        <v>355</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13307,13 +13349,13 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>609</v>
+        <v>356</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
@@ -13322,16 +13364,16 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>614</v>
+        <v>357</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>615</v>
+        <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13339,18 +13381,18 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>87</v>
@@ -13362,18 +13404,20 @@
         <v>80</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>167</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>168</v>
+        <v>361</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13422,7 +13466,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>170</v>
+        <v>364</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13434,10 +13478,10 @@
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>171</v>
+        <v>365</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>80</v>
@@ -13446,7 +13490,7 @@
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>80</v>
+        <v>366</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13454,18 +13498,18 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>146</v>
+        <v>368</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>79</v>
@@ -13477,19 +13521,19 @@
         <v>80</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>175</v>
+        <v>370</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>149</v>
+        <v>371</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13539,7 +13583,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>177</v>
+        <v>372</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13551,10 +13595,10 @@
         <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>171</v>
+        <v>373</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>80</v>
@@ -13563,7 +13607,7 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>80</v>
+        <v>374</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13571,14 +13615,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>557</v>
+        <v>80</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13591,26 +13635,22 @@
         <v>80</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>558</v>
+        <v>376</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>80</v>
       </c>
@@ -13658,7 +13698,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>560</v>
+        <v>378</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13670,10 +13710,10 @@
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>130</v>
+        <v>379</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>80</v>
@@ -13682,7 +13722,7 @@
         <v>80</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -13690,10 +13730,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>619</v>
+        <v>594</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>619</v>
+        <v>594</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13701,10 +13741,10 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>80</v>
@@ -13713,23 +13753,19 @@
         <v>80</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>620</v>
+        <v>382</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>80</v>
       </c>
@@ -13753,13 +13789,13 @@
         <v>80</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>80</v>
@@ -13777,13 +13813,13 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>619</v>
+        <v>384</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>80</v>
@@ -13792,16 +13828,16 @@
         <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>624</v>
+        <v>385</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>625</v>
+        <v>80</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>626</v>
+        <v>386</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>80</v>
@@ -13809,10 +13845,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>627</v>
+        <v>595</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>627</v>
+        <v>595</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13832,22 +13868,20 @@
         <v>80</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>299</v>
+        <v>223</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>628</v>
+        <v>388</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>630</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>631</v>
+        <v>390</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -13896,7 +13930,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>627</v>
+        <v>391</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13911,16 +13945,16 @@
         <v>99</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>632</v>
+        <v>392</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>633</v>
+        <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>634</v>
+        <v>393</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -13928,14 +13962,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>635</v>
+        <v>596</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>635</v>
+        <v>596</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>636</v>
+        <v>80</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13954,18 +13988,20 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>637</v>
+        <v>395</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>638</v>
+        <v>597</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>639</v>
+        <v>598</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>80</v>
       </c>
@@ -14013,7 +14049,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>635</v>
+        <v>596</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14028,7 +14064,7 @@
         <v>99</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>641</v>
+        <v>400</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>171</v>
@@ -14037,7 +14073,7 @@
         <v>80</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>642</v>
+        <v>600</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14045,10 +14081,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>643</v>
+        <v>601</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>643</v>
+        <v>601</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14056,7 +14092,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>87</v>
@@ -14068,22 +14104,20 @@
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>231</v>
+        <v>432</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>644</v>
+        <v>602</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>646</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>647</v>
+        <v>604</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14132,7 +14166,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>643</v>
+        <v>601</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14147,16 +14181,16 @@
         <v>99</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>603</v>
+        <v>437</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>648</v>
+        <v>171</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>80</v>
+        <v>605</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14164,10 +14198,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>649</v>
+        <v>606</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>649</v>
+        <v>606</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14178,31 +14212,29 @@
         <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>547</v>
+        <v>107</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>650</v>
+        <v>404</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>652</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>653</v>
+        <v>608</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14227,13 +14259,13 @@
         <v>80</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>80</v>
+        <v>408</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>80</v>
+        <v>409</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14251,13 +14283,13 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>649</v>
+        <v>606</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>80</v>
@@ -14266,7 +14298,7 @@
         <v>99</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>654</v>
+        <v>410</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>171</v>
@@ -14275,7 +14307,7 @@
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>80</v>
+        <v>609</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -14283,10 +14315,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>655</v>
+        <v>610</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>655</v>
+        <v>610</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14309,16 +14341,18 @@
         <v>80</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>168</v>
+        <v>611</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>169</v>
+        <v>612</v>
       </c>
       <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>80</v>
       </c>
@@ -14366,7 +14400,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>170</v>
+        <v>610</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14375,22 +14409,22 @@
         <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>80</v>
+        <v>614</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AL102" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>80</v>
+        <v>616</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>80</v>
@@ -14398,21 +14432,21 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>656</v>
+        <v>617</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>656</v>
+        <v>617</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>80</v>
@@ -14424,17 +14458,15 @@
         <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>132</v>
+        <v>223</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>174</v>
+        <v>618</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14483,25 +14515,25 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>177</v>
+        <v>617</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AL103" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>80</v>
@@ -14515,14 +14547,14 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>657</v>
+        <v>621</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>657</v>
+        <v>621</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>557</v>
+        <v>80</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14535,25 +14567,25 @@
         <v>80</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>132</v>
+        <v>547</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>558</v>
+        <v>622</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>559</v>
+        <v>623</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>149</v>
+        <v>624</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>150</v>
+        <v>625</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14602,7 +14634,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>560</v>
+        <v>621</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14614,13 +14646,13 @@
         <v>80</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>130</v>
+        <v>626</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>80</v>
+        <v>627</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>80</v>
@@ -14634,10 +14666,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>658</v>
+        <v>628</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>658</v>
+        <v>628</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14645,7 +14677,7 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>87</v>
@@ -14657,20 +14689,18 @@
         <v>80</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>659</v>
+        <v>167</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>660</v>
+        <v>168</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>662</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -14719,10 +14749,10 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>658</v>
+        <v>170</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>87</v>
@@ -14731,19 +14761,19 @@
         <v>80</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>663</v>
+        <v>80</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -14751,21 +14781,21 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>664</v>
+        <v>629</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>664</v>
+        <v>629</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>80</v>
@@ -14774,18 +14804,20 @@
         <v>80</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>665</v>
+        <v>174</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -14810,57 +14842,1352 @@
         <v>80</v>
       </c>
       <c r="X106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X117" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y106" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
+      <c r="Y117" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK106" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AL106" t="s" s="2">
+      <c r="AK117" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AL117" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AM106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO106" t="s" s="2">
+      <c r="AM117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO117" t="s" s="2">
         <v>80</v>
       </c>
     </row>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:28:06+00:00</t>
+    <t>2023-04-01T08:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4384" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3975" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:29:12+00:00</t>
+    <t>2023-04-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1762,13 +1762,6 @@
     <t>Used to determine which contact person is the most relevant to approach, depending on circumstances.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;code value="N"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
@@ -1779,42 +1772,6 @@
   </si>
   <si>
     <t>NK1-7, NK1-3</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.id</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.extension</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.id</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.extension</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.system</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0131</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.version</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.code</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.display</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.text</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -2421,11 +2378,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO117"/>
+  <dimension ref="A1:AO106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.59375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.59375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.7109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.23828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -11397,10 +11354,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>80</v>
@@ -11432,7 +11389,7 @@
         <v>80</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>565</v>
+        <v>80</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>80</v>
@@ -11450,10 +11407,10 @@
         <v>196</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11486,7 +11443,7 @@
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>171</v>
@@ -11495,7 +11452,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -11503,10 +11460,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11529,16 +11486,18 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>167</v>
+        <v>331</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>168</v>
+        <v>570</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>169</v>
+        <v>571</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11586,7 +11545,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>170</v>
+        <v>569</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11598,19 +11557,19 @@
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL78" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AL78" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>80</v>
+        <v>573</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11618,21 +11577,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>80</v>
@@ -11644,17 +11603,15 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11691,31 +11648,31 @@
         <v>80</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>171</v>
@@ -11735,14 +11692,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11758,23 +11715,21 @@
         <v>80</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>251</v>
+        <v>174</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>252</v>
+        <v>175</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
       </c>
@@ -11810,19 +11765,19 @@
         <v>80</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11834,10 +11789,10 @@
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>256</v>
+        <v>171</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>80</v>
@@ -11846,7 +11801,7 @@
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -11854,10 +11809,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11874,22 +11829,26 @@
         <v>80</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>168</v>
+        <v>342</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
       </c>
@@ -11913,13 +11872,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -11937,7 +11896,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>170</v>
+        <v>348</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11949,10 +11908,10 @@
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>171</v>
+        <v>349</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>80</v>
@@ -11961,7 +11920,7 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -11969,21 +11928,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -11992,21 +11951,23 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>174</v>
+        <v>352</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>175</v>
+        <v>353</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
       </c>
@@ -12042,34 +12003,34 @@
         <v>80</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>177</v>
+        <v>356</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>171</v>
+        <v>357</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>80</v>
@@ -12078,7 +12039,7 @@
         <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12086,18 +12047,18 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>87</v>
@@ -12112,20 +12073,18 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>264</v>
+        <v>361</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>265</v>
+        <v>362</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>80</v>
       </c>
@@ -12134,7 +12093,7 @@
         <v>80</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>576</v>
+        <v>80</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>80</v>
@@ -12173,7 +12132,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>269</v>
+        <v>364</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12188,7 +12147,7 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>270</v>
+        <v>365</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>80</v>
@@ -12197,7 +12156,7 @@
         <v>80</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>271</v>
+        <v>366</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12205,21 +12164,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -12234,13 +12193,13 @@
         <v>167</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>274</v>
+        <v>369</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>275</v>
+        <v>370</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>276</v>
+        <v>371</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12290,13 +12249,13 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>277</v>
+        <v>372</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
@@ -12305,7 +12264,7 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>278</v>
+        <v>373</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>80</v>
@@ -12314,7 +12273,7 @@
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>279</v>
+        <v>374</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12322,10 +12281,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12336,7 +12295,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12348,18 +12307,16 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>282</v>
+        <v>376</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>283</v>
+        <v>377</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>284</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>80</v>
       </c>
@@ -12407,13 +12364,13 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>285</v>
+        <v>378</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
@@ -12422,7 +12379,7 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>286</v>
+        <v>379</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>80</v>
@@ -12431,7 +12388,7 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>287</v>
+        <v>380</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
@@ -12439,10 +12396,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12453,7 +12410,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>80</v>
@@ -12468,15 +12425,13 @@
         <v>167</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>290</v>
+        <v>382</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>291</v>
+        <v>383</v>
       </c>
       <c r="N86" s="2"/>
-      <c r="O86" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>80</v>
       </c>
@@ -12524,13 +12479,13 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>294</v>
+        <v>384</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>80</v>
@@ -12539,7 +12494,7 @@
         <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>295</v>
+        <v>385</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
@@ -12548,7 +12503,7 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>296</v>
+        <v>386</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -12556,10 +12511,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12582,19 +12537,17 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>299</v>
+        <v>223</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>300</v>
+        <v>388</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>303</v>
+        <v>390</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12643,7 +12596,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>304</v>
+        <v>391</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12658,7 +12611,7 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>305</v>
+        <v>392</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>80</v>
@@ -12667,7 +12620,7 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>306</v>
+        <v>393</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -12675,10 +12628,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12689,7 +12642,7 @@
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>80</v>
@@ -12698,22 +12651,22 @@
         <v>80</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>167</v>
+        <v>395</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>309</v>
+        <v>584</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>310</v>
+        <v>585</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>311</v>
+        <v>586</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>312</v>
+        <v>399</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -12762,13 +12715,13 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>314</v>
+        <v>583</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
@@ -12777,16 +12730,16 @@
         <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>315</v>
+        <v>400</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>316</v>
+        <v>587</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -12794,10 +12747,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12820,17 +12773,17 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>331</v>
+        <v>432</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -12879,7 +12832,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12894,7 +12847,7 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>336</v>
+        <v>437</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>171</v>
@@ -12903,7 +12856,7 @@
         <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -12911,10 +12864,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12937,16 +12890,18 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>168</v>
+        <v>404</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>169</v>
+        <v>594</v>
       </c>
       <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
       </c>
@@ -12970,13 +12925,13 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>80</v>
+        <v>408</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>80</v>
+        <v>409</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -12994,7 +12949,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>170</v>
+        <v>593</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13006,19 +12961,19 @@
         <v>80</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL90" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AL90" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>80</v>
+        <v>596</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13026,21 +12981,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>80</v>
@@ -13052,18 +13007,18 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>132</v>
+        <v>231</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>174</v>
+        <v>598</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13099,43 +13054,43 @@
         <v>80</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>177</v>
+        <v>597</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>80</v>
+        <v>601</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AL91" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AL91" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>80</v>
+        <v>603</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13143,10 +13098,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13163,26 +13118,22 @@
         <v>80</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>342</v>
+        <v>605</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>80</v>
       </c>
@@ -13206,13 +13157,13 @@
         <v>80</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -13230,7 +13181,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>348</v>
+        <v>604</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13245,16 +13196,16 @@
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>349</v>
+        <v>607</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13262,10 +13213,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13276,7 +13227,7 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>80</v>
@@ -13285,22 +13236,22 @@
         <v>80</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>167</v>
+        <v>547</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>352</v>
+        <v>609</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>353</v>
+        <v>610</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>354</v>
+        <v>611</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>355</v>
+        <v>612</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13349,13 +13300,13 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>356</v>
+        <v>608</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
@@ -13364,16 +13315,16 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>357</v>
+        <v>613</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>80</v>
+        <v>614</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>358</v>
+        <v>80</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13381,18 +13332,18 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>360</v>
+        <v>80</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>87</v>
@@ -13404,20 +13355,18 @@
         <v>80</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>167</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>361</v>
+        <v>168</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13466,7 +13415,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>364</v>
+        <v>170</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13478,10 +13427,10 @@
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>365</v>
+        <v>171</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>80</v>
@@ -13490,7 +13439,7 @@
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13498,18 +13447,18 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>368</v>
+        <v>146</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>79</v>
@@ -13521,19 +13470,19 @@
         <v>80</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>369</v>
+        <v>174</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>370</v>
+        <v>175</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>371</v>
+        <v>149</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13583,7 +13532,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>372</v>
+        <v>177</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13595,10 +13544,10 @@
         <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>373</v>
+        <v>171</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>80</v>
@@ -13607,7 +13556,7 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13615,14 +13564,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>80</v>
+        <v>557</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13635,22 +13584,26 @@
         <v>80</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>376</v>
+        <v>558</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
       </c>
@@ -13698,7 +13651,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>378</v>
+        <v>560</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13710,10 +13663,10 @@
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>379</v>
+        <v>130</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>80</v>
@@ -13722,7 +13675,7 @@
         <v>80</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -13730,10 +13683,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13741,10 +13694,10 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>80</v>
@@ -13753,19 +13706,23 @@
         <v>80</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>382</v>
+        <v>619</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>620</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>622</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>80</v>
       </c>
@@ -13789,13 +13746,13 @@
         <v>80</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>80</v>
@@ -13813,13 +13770,13 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>384</v>
+        <v>618</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>80</v>
@@ -13828,16 +13785,16 @@
         <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>385</v>
+        <v>623</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>80</v>
+        <v>624</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>386</v>
+        <v>625</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>80</v>
@@ -13845,10 +13802,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13868,20 +13825,22 @@
         <v>80</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>388</v>
+        <v>627</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>628</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="O98" t="s" s="2">
-        <v>390</v>
+        <v>630</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -13930,7 +13889,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>391</v>
+        <v>626</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13945,16 +13904,16 @@
         <v>99</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>392</v>
+        <v>631</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>80</v>
+        <v>632</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>393</v>
+        <v>633</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -13962,14 +13921,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>596</v>
+        <v>634</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>596</v>
+        <v>634</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>80</v>
+        <v>635</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13988,20 +13947,18 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>395</v>
+        <v>636</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>597</v>
+        <v>637</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>598</v>
+        <v>638</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>80</v>
       </c>
@@ -14049,7 +14006,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>596</v>
+        <v>634</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14064,7 +14021,7 @@
         <v>99</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>400</v>
+        <v>640</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>171</v>
@@ -14073,7 +14030,7 @@
         <v>80</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>600</v>
+        <v>641</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14081,10 +14038,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>601</v>
+        <v>642</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>601</v>
+        <v>642</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14092,7 +14049,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>87</v>
@@ -14104,20 +14061,22 @@
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>432</v>
+        <v>231</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>602</v>
+        <v>643</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>644</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="O100" t="s" s="2">
-        <v>604</v>
+        <v>646</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14166,7 +14125,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>601</v>
+        <v>642</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14181,16 +14140,16 @@
         <v>99</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>437</v>
+        <v>602</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>171</v>
+        <v>647</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>605</v>
+        <v>80</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14198,10 +14157,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>606</v>
+        <v>648</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>606</v>
+        <v>648</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14212,29 +14171,31 @@
         <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>107</v>
+        <v>547</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>404</v>
+        <v>649</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>651</v>
+      </c>
       <c r="O101" t="s" s="2">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14259,13 +14220,13 @@
         <v>80</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14283,13 +14244,13 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>606</v>
+        <v>648</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>80</v>
@@ -14298,7 +14259,7 @@
         <v>99</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>410</v>
+        <v>653</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>171</v>
@@ -14307,7 +14268,7 @@
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>609</v>
+        <v>80</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -14315,10 +14276,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>610</v>
+        <v>654</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>610</v>
+        <v>654</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14341,18 +14302,16 @@
         <v>80</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>611</v>
+        <v>168</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>612</v>
+        <v>169</v>
       </c>
       <c r="N102" s="2"/>
-      <c r="O102" t="s" s="2">
-        <v>613</v>
-      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>80</v>
       </c>
@@ -14400,7 +14359,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>610</v>
+        <v>170</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14409,22 +14368,22 @@
         <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>614</v>
+        <v>80</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>615</v>
+        <v>171</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>616</v>
+        <v>80</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>80</v>
@@ -14432,21 +14391,21 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>617</v>
+        <v>655</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>617</v>
+        <v>655</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>80</v>
@@ -14458,15 +14417,17 @@
         <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>618</v>
+        <v>174</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14515,25 +14476,25 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>617</v>
+        <v>177</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>620</v>
+        <v>171</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>80</v>
@@ -14547,14 +14508,14 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>621</v>
+        <v>656</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>621</v>
+        <v>656</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>80</v>
+        <v>557</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14567,25 +14528,25 @@
         <v>80</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>547</v>
+        <v>132</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>622</v>
+        <v>558</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>623</v>
+        <v>559</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>624</v>
+        <v>149</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>625</v>
+        <v>150</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14634,7 +14595,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>621</v>
+        <v>560</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14646,13 +14607,13 @@
         <v>80</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>626</v>
+        <v>130</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>627</v>
+        <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>80</v>
@@ -14666,10 +14627,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14677,7 +14638,7 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>87</v>
@@ -14689,18 +14650,20 @@
         <v>80</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>167</v>
+        <v>658</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>168</v>
+        <v>659</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>660</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>661</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -14749,10 +14712,10 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>170</v>
+        <v>657</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>87</v>
@@ -14761,19 +14724,19 @@
         <v>80</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL105" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AL105" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>80</v>
+        <v>662</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -14781,21 +14744,21 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>629</v>
+        <v>663</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>629</v>
+        <v>663</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>80</v>
@@ -14804,20 +14767,18 @@
         <v>80</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>174</v>
+        <v>664</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>665</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -14842,13 +14803,13 @@
         <v>80</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>80</v>
+        <v>665</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>80</v>
+        <v>666</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>80</v>
@@ -14866,26 +14827,26 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>177</v>
+        <v>663</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK106" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AL106" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AL106" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM106" t="s" s="2">
         <v>80</v>
       </c>
@@ -14893,1301 +14854,6 @@
         <v>80</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O110" s="2"/>
-      <c r="P110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="P111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O114" s="2"/>
-      <c r="P114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO117" t="s" s="2">
         <v>80</v>
       </c>
     </row>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:49:37+00:00</t>
+    <t>2023-04-01T08:50:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:50:39+00:00</t>
+    <t>2023-04-03T09:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:35:38+00:00</t>
+    <t>2023-04-03T09:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$106</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:37:11+00:00</t>
+    <t>2023-04-03T10:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2205,6 +2208,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2548,7 +2566,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>9</v>
       </c>
@@ -2663,7 +2681,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -2780,7 +2798,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -2895,7 +2913,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -3012,7 +3030,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -3129,7 +3147,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -3246,7 +3264,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -3363,7 +3381,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -3476,7 +3494,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -3593,7 +3611,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -3712,7 +3730,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>152</v>
       </c>
@@ -3827,7 +3845,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -3928,7 +3946,7 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>159</v>
@@ -3946,7 +3964,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>165</v>
       </c>
@@ -4061,7 +4079,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
@@ -4178,7 +4196,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>178</v>
       </c>
@@ -4297,7 +4315,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>189</v>
       </c>
@@ -4416,7 +4434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>201</v>
       </c>
@@ -4535,7 +4553,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>212</v>
       </c>
@@ -4554,7 +4572,7 @@
         <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -4652,7 +4670,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>221</v>
       </c>
@@ -4767,7 +4785,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>229</v>
       </c>
@@ -4884,7 +4902,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>238</v>
       </c>
@@ -5003,7 +5021,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>240</v>
       </c>
@@ -5118,7 +5136,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>241</v>
       </c>
@@ -5235,7 +5253,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>242</v>
       </c>
@@ -5354,7 +5372,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>243</v>
       </c>
@@ -5473,7 +5491,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>244</v>
       </c>
@@ -5588,7 +5606,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>246</v>
       </c>
@@ -5705,7 +5723,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>248</v>
       </c>
@@ -5824,7 +5842,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>258</v>
       </c>
@@ -5939,7 +5957,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>260</v>
       </c>
@@ -6056,7 +6074,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>262</v>
       </c>
@@ -6175,7 +6193,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>272</v>
       </c>
@@ -6292,7 +6310,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>280</v>
       </c>
@@ -6409,7 +6427,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>288</v>
       </c>
@@ -6526,7 +6544,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>297</v>
       </c>
@@ -6645,7 +6663,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>307</v>
       </c>
@@ -6764,7 +6782,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>317</v>
       </c>
@@ -6883,7 +6901,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>319</v>
       </c>
@@ -7000,7 +7018,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>320</v>
       </c>
@@ -7115,7 +7133,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>321</v>
       </c>
@@ -7232,7 +7250,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>322</v>
       </c>
@@ -7353,7 +7371,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>330</v>
       </c>
@@ -7472,7 +7490,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>339</v>
       </c>
@@ -7587,7 +7605,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>340</v>
       </c>
@@ -7704,7 +7722,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>341</v>
       </c>
@@ -7823,7 +7841,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>351</v>
       </c>
@@ -7942,7 +7960,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>359</v>
       </c>
@@ -8059,7 +8077,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>367</v>
       </c>
@@ -8176,7 +8194,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>375</v>
       </c>
@@ -8291,7 +8309,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>381</v>
       </c>
@@ -8406,7 +8424,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>387</v>
       </c>
@@ -8523,7 +8541,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>394</v>
       </c>
@@ -8542,7 +8560,7 @@
         <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>80</v>
@@ -8642,7 +8660,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>403</v>
       </c>
@@ -8761,7 +8779,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>413</v>
       </c>
@@ -8880,7 +8898,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>423</v>
       </c>
@@ -8999,7 +9017,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>431</v>
       </c>
@@ -9018,7 +9036,7 @@
         <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>80</v>
@@ -9118,7 +9136,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>440</v>
       </c>
@@ -9233,7 +9251,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>441</v>
       </c>
@@ -9350,7 +9368,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>442</v>
       </c>
@@ -9469,7 +9487,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>452</v>
       </c>
@@ -9586,7 +9604,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>461</v>
       </c>
@@ -9705,7 +9723,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>468</v>
       </c>
@@ -9820,7 +9838,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>475</v>
       </c>
@@ -9935,7 +9953,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>483</v>
       </c>
@@ -10052,7 +10070,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>492</v>
       </c>
@@ -10167,7 +10185,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>499</v>
       </c>
@@ -10282,7 +10300,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>507</v>
       </c>
@@ -10399,7 +10417,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>514</v>
       </c>
@@ -10516,7 +10534,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>521</v>
       </c>
@@ -10633,7 +10651,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>530</v>
       </c>
@@ -10752,7 +10770,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>538</v>
       </c>
@@ -10871,7 +10889,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>546</v>
       </c>
@@ -10890,7 +10908,7 @@
         <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>80</v>
@@ -10990,7 +11008,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>554</v>
       </c>
@@ -11105,7 +11123,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>555</v>
       </c>
@@ -11222,7 +11240,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>556</v>
       </c>
@@ -11341,7 +11359,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>561</v>
       </c>
@@ -11458,7 +11476,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>569</v>
       </c>
@@ -11575,7 +11593,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>574</v>
       </c>
@@ -11690,7 +11708,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>575</v>
       </c>
@@ -11807,7 +11825,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>576</v>
       </c>
@@ -11926,7 +11944,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>577</v>
       </c>
@@ -12045,7 +12063,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>578</v>
       </c>
@@ -12162,7 +12180,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>579</v>
       </c>
@@ -12279,7 +12297,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>580</v>
       </c>
@@ -12394,7 +12412,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
         <v>581</v>
       </c>
@@ -12509,7 +12527,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
         <v>582</v>
       </c>
@@ -12626,7 +12644,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
         <v>583</v>
       </c>
@@ -12645,7 +12663,7 @@
         <v>79</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>80</v>
@@ -12745,7 +12763,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
         <v>588</v>
       </c>
@@ -12862,7 +12880,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
         <v>593</v>
       </c>
@@ -12979,7 +12997,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
         <v>597</v>
       </c>
@@ -13096,7 +13114,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
         <v>604</v>
       </c>
@@ -13211,7 +13229,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
         <v>608</v>
       </c>
@@ -13330,7 +13348,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
         <v>615</v>
       </c>
@@ -13445,7 +13463,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
         <v>616</v>
       </c>
@@ -13562,7 +13580,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
         <v>617</v>
       </c>
@@ -13681,7 +13699,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
         <v>618</v>
       </c>
@@ -13800,7 +13818,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
         <v>626</v>
       </c>
@@ -13919,7 +13937,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
         <v>634</v>
       </c>
@@ -14036,7 +14054,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
         <v>642</v>
       </c>
@@ -14155,7 +14173,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
         <v>648</v>
       </c>
@@ -14274,7 +14292,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
         <v>654</v>
       </c>
@@ -14389,7 +14407,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
         <v>655</v>
       </c>
@@ -14506,7 +14524,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
         <v>656</v>
       </c>
@@ -14625,7 +14643,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
         <v>657</v>
       </c>
@@ -14742,7 +14760,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
         <v>663</v>
       </c>
@@ -14858,6 +14876,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO106">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI105">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:19:29+00:00</t>
+    <t>2023-04-03T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:20:09+00:00</t>
+    <t>2023-04-04T06:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:46:45+00:00</t>
+    <t>2023-04-04T06:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:47:21+00:00</t>
+    <t>2023-04-04T08:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:23:07+00:00</t>
+    <t>2023-04-04T08:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:37:07+00:00</t>
+    <t>2023-04-04T09:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:08:50+00:00</t>
+    <t>2023-04-04T09:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:09:26+00:00</t>
+    <t>2023-04-04T09:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:19:23+00:00</t>
+    <t>2023-04-04T09:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:25:44+00:00</t>
+    <t>2023-04-04T10:05:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:05:22+00:00</t>
+    <t>2023-04-04T10:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:05:29+00:00</t>
+    <t>2023-04-04T10:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:21:49+00:00</t>
+    <t>2023-04-04T10:30:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:30:43+00:00</t>
+    <t>2023-04-04T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:10+00:00</t>
+    <t>2023-04-04T10:41:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:37+00:00</t>
+    <t>2023-04-04T13:12:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:12:16+00:00</t>
+    <t>2023-04-04T13:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:12:12+00:00</t>
+    <t>2023-04-17T11:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -661,7 +661,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/hiv-cbs/identifier/nid</t>
+    <t>http://openhie.org/fhir/training-solution-1/identifier/nid</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -998,7 +998,7 @@
     <t>Patient.identifier:MR.system</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/hiv-cbs/identifier/mr</t>
+    <t>http://openhie.org/fhir/training-solution-1/identifier/mr</t>
   </si>
   <si>
     <t>Patient.identifier:MR.value</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:49:04+00:00</t>
+    <t>2023-04-17T12:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3975" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3977" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:05:39+00:00</t>
+    <t>2023-05-26T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -2228,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -2315,77 +2315,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>35</v>
       </c>
     </row>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:19+00:00</t>
+    <t>2023-05-26T12:35:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:50+00:00</t>
+    <t>2023-05-26T12:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:45:45+00:00</t>
+    <t>2023-05-26T12:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:47:23+00:00</t>
+    <t>2023-05-26T13:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:04:11+00:00</t>
+    <t>2023-05-26T13:05:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:05:32+00:00</t>
+    <t>2023-05-26T14:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:47:38+00:00</t>
+    <t>2023-05-26T14:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:52:17+00:00</t>
+    <t>2023-05-26T14:59:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:59:52+00:00</t>
+    <t>2023-05-26T15:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3977" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3978" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:03:26+00:00</t>
+    <t>2023-05-29T05:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -508,11 +508,11 @@
     <t>Patients are almost always assigned specific numerical identifiers.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
-    <t>openAtEnd</t>
+    <t>Slice based on the type of identifier.</t>
   </si>
   <si>
     <t>id</t>
@@ -3815,12 +3815,14 @@
       <c r="AB12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AC12" s="2"/>
+      <c r="AC12" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="AD12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>152</v>

--- a/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Add-laboratory-definitions/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:44:52+00:00</t>
+    <t>2023-06-13T16:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
